--- a/Kamp 2026 prijave_nastavnici - v2.xlsx
+++ b/Kamp 2026 prijave_nastavnici - v2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\APLIKACIJE\Nastavnici\nastavnici_2026_Pula\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{59DC875F-CB5B-4CEF-9EA8-575E1269C5DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD13BD73-39FF-47B2-A75E-F52F7E5E7EA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="24220" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,12 +16,11 @@
     <sheet name="List1" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1163" uniqueCount="778">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1177" uniqueCount="786">
   <si>
     <t>Ime</t>
   </si>
@@ -2355,13 +2354,37 @@
   </si>
   <si>
     <t>rbr</t>
+  </si>
+  <si>
+    <t>Filipina</t>
+  </si>
+  <si>
+    <t>Jukičić</t>
+  </si>
+  <si>
+    <t>Oš Granešina</t>
+  </si>
+  <si>
+    <t>filipina.jukicic@skole.hr</t>
+  </si>
+  <si>
+    <t>Martina</t>
+  </si>
+  <si>
+    <t>Kolovrat</t>
+  </si>
+  <si>
+    <t>Katolička osnovna škola, Šibenik</t>
+  </si>
+  <si>
+    <t>martina.kolovrat1@skole.hr</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -2392,8 +2415,31 @@
       <charset val="238"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF434343"/>
+      <name val="Roboto"/>
+      <charset val="238"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2406,8 +2452,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8F9FA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -2415,11 +2473,102 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFFFFFFF"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFF8F9FA"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF8F9FA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFF8F9FA"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF8F9FA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF442F65"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFF8F9FA"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF8F9FA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFF8F9FA"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFF8F9FA"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF442F65"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFF8F9FA"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF442F65"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF442F65"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF442F65"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2431,27 +2580,36 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hiperveza" xfId="1" builtinId="8"/>
     <cellStyle name="Normalno" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="4">
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF5B3F86"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF5B3F86"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF5B3F86"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF5B3F86"/>
-        </bottom>
-      </border>
-    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -2476,13 +2634,29 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF5B3F86"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF5B3F86"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF5B3F86"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF5B3F86"/>
+        </bottom>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Form responses 1-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="0"/>
-      <tableStyleElement type="headerRow" dxfId="3"/>
-      <tableStyleElement type="firstRowStripe" dxfId="2"/>
-      <tableStyleElement type="secondRowStripe" dxfId="1"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="3"/>
+      <tableStyleElement type="headerRow" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="secondRowStripe" dxfId="0"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -2694,7 +2868,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A20DB09A-833D-4359-82E2-9B48D569BE70}">
-  <dimension ref="A1:J138"/>
+  <dimension ref="A1:J140"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="15.54296875" bestFit="1" customWidth="1"/>
@@ -6869,7 +7043,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="138" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:10" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>137</v>
       </c>
@@ -6898,7 +7072,71 @@
         <v>16</v>
       </c>
     </row>
+    <row r="139" spans="1:10" ht="23" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A139">
+        <v>138</v>
+      </c>
+      <c r="B139" s="5" t="s">
+        <v>778</v>
+      </c>
+      <c r="C139" s="6" t="s">
+        <v>779</v>
+      </c>
+      <c r="D139" s="6" t="s">
+        <v>780</v>
+      </c>
+      <c r="E139" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="F139" s="6">
+        <v>994669569</v>
+      </c>
+      <c r="G139" s="11" t="s">
+        <v>781</v>
+      </c>
+      <c r="H139" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I139" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J139" s="7"/>
+    </row>
+    <row r="140" spans="1:10" ht="18.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A140">
+        <v>139</v>
+      </c>
+      <c r="B140" s="8" t="s">
+        <v>782</v>
+      </c>
+      <c r="C140" s="9" t="s">
+        <v>783</v>
+      </c>
+      <c r="D140" s="9" t="s">
+        <v>784</v>
+      </c>
+      <c r="E140" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F140" s="9">
+        <v>989306665</v>
+      </c>
+      <c r="G140" s="12" t="s">
+        <v>785</v>
+      </c>
+      <c r="H140" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="I140" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J140" s="10"/>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="G139" r:id="rId1" xr:uid="{4FF45DD5-2911-4FD0-AB42-72BB0CF3B948}"/>
+    <hyperlink ref="G140" r:id="rId2" xr:uid="{3A529E3E-B877-4FCE-A1DA-BF5FF1D4FDC0}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>